--- a/supplier_management_forms/030_supplier_standardization_application_form--supplier_management_forms.xlsx
+++ b/supplier_management_forms/030_supplier_standardization_application_form--supplier_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'3-1',_'name':_'iso_9001',_'label':_'iso_9001',_'value':_1}</t>
+          <t>iso_9001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '3-1', 'name': 'iso_9001', 'label': 'ISO 9001', 'value': 1}</t>
+          <t>ISO 9001</t>
         </is>
       </c>
     </row>
@@ -826,148 +826,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'3-2',_'name':_'iso_13485',_'label':_'iso_13485',_'value':_2}</t>
+          <t>iso_13485</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '3-2', 'name': 'iso_13485', 'label': 'ISO 13485', 'value': 2}</t>
+          <t>ISO 13485</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>certifications_choices</t>
+          <t>agreements_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'3-1-1',_'name':_'iso_9001',_'label':_'iso_9001',_'value':_1}</t>
+          <t>master_agreement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '3-1-1', 'name': 'iso_9001', 'label': 'ISO 9001', 'value': 1}</t>
+          <t>Master Agreement</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>certifications_choices</t>
+          <t>agreements_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'3-1-2',_'name':_'iso_13485',_'label':_'iso_13485',_'value':_2}</t>
+          <t>annex_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '3-1-2', 'name': 'iso_13485', 'label': 'ISO 13485', 'value': 2}</t>
+          <t>Annex 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>agreements_choices</t>
+          <t>onboarding_process_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'4-1',_'name':_'master_agreement',_'label':_'master_agreement',_'value':_1}</t>
+          <t>onboarding_process_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '4-1', 'name': 'master_agreement', 'label': 'Master Agreement', 'value': 1}</t>
+          <t>Onboarding Process 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>agreements_choices</t>
+          <t>onboarding_process_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'4-2',_'name':_'annex_1',_'label':_'annex_1',_'value':_2}</t>
+          <t>onboarding_process_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '4-2', 'name': 'annex_1', 'label': 'Annex 1', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>agreements_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_'4-1-1',_'name':_'master_agreement',_'label':_'master_agreement',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': '4-1-1', 'name': 'master_agreement', 'label': 'Master Agreement', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>agreements_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_'4-1-2',_'name':_'annex_1',_'label':_'annex_1',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': '4-1-2', 'name': 'annex_1', 'label': 'Annex 1', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>onboarding_process_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_'10-1',_'name':_'onboarding_process_1',_'label':_'onboarding_process_1',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': '10-1', 'name': 'onboarding_process_1', 'label': 'Onboarding Process 1', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>onboarding_process_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_'10-2',_'name':_'onboarding_process_2',_'label':_'onboarding_process_2',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': '10-2', 'name': 'onboarding_process_2', 'label': 'Onboarding Process 2', 'value': 2}</t>
+          <t>Onboarding Process 2</t>
         </is>
       </c>
     </row>
